--- a/data/trans_camb/P38B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,89; -5,9</t>
+          <t>-21,39; -6,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 17,82</t>
+          <t>7,57; 18,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,29; -8,26</t>
+          <t>-20,59; -7,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 13,13</t>
+          <t>5,18; 12,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -9,31</t>
+          <t>-18,88; -9,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 13,79</t>
+          <t>7,35; 13,99</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,48; -7,43</t>
+          <t>-24,2; -8,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 22,46</t>
+          <t>8,69; 22,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,37; -9,65</t>
+          <t>-22,62; -9,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 15,28</t>
+          <t>5,5; 15,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,82; -10,99</t>
+          <t>-21,34; -10,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,65; 16,43</t>
+          <t>8,32; 16,78</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,81</t>
+          <t>-2,56; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -5,58</t>
+          <t>-18,23; -4,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 4,62</t>
+          <t>-1,36; 4,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; -5,35</t>
+          <t>-13,08; -5,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,09</t>
+          <t>-0,73; 4,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; -6,76</t>
+          <t>-14,42; -6,75</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,82</t>
+          <t>-2,89; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -6,53</t>
+          <t>-20,99; -5,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,06</t>
+          <t>-1,43; 5,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,95; -5,82</t>
+          <t>-13,73; -5,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,62</t>
+          <t>-0,8; 4,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -7,59</t>
+          <t>-15,84; -7,6</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 10,17</t>
+          <t>0,14; 10,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,83</t>
+          <t>4,05; 14,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 8,36</t>
+          <t>-0,71; 8,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,07</t>
+          <t>4,82; 12,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,87</t>
+          <t>1,29; 7,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,6; 12,19</t>
+          <t>5,86; 12,44</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 12,52</t>
+          <t>0,15; 12,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 17,15</t>
+          <t>4,69; 17,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 9,75</t>
+          <t>-0,73; 10,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 15,46</t>
+          <t>5,29; 15,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,36</t>
+          <t>1,46; 9,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 14,5</t>
+          <t>6,64; 14,76</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 20,03</t>
+          <t>9,25; 20,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 18,42</t>
+          <t>1,3; 17,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,26</t>
+          <t>2,0; 11,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 10,09</t>
+          <t>-36,88; 10,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 13,81</t>
+          <t>7,05; 13,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 11,6</t>
+          <t>-22,16; 11,31</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,31; 27,66</t>
+          <t>11,47; 27,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 24,85</t>
+          <t>1,9; 24,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,84</t>
+          <t>2,33; 13,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 12,02</t>
+          <t>-43,06; 12,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,78</t>
+          <t>8,4; 17,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 14,44</t>
+          <t>-26,65; 14,09</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 1,66</t>
+          <t>-13,66; 1,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 5,64</t>
+          <t>-9,61; 5,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 1,97</t>
+          <t>-8,58; 1,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 1,44</t>
+          <t>-8,79; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 0,24</t>
+          <t>-9,42; 0,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,35</t>
+          <t>-7,16; 2,3</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 2,43</t>
+          <t>-15,77; 2,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 7,09</t>
+          <t>-11,02; 6,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 2,26</t>
+          <t>-9,18; 1,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 1,33</t>
+          <t>-9,52; 1,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 0,24</t>
+          <t>-10,52; 0,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 2,72</t>
+          <t>-8,06; 2,72</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -0,99</t>
+          <t>-13,54; -0,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,04; 13,02</t>
+          <t>3,34; 12,87</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 4,45</t>
+          <t>-7,25; 4,19</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,9; 14,0</t>
+          <t>4,82; 13,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,56; -0,05</t>
+          <t>-8,76; -0,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,56; 11,95</t>
+          <t>5,26; 11,77</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -1,21</t>
+          <t>-15,05; -0,88</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,44; 15,56</t>
+          <t>3,75; 15,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 5,19</t>
+          <t>-8,01; 4,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,34; 16,56</t>
+          <t>5,25; 16,23</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -0,08</t>
+          <t>-9,71; -0,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,04</t>
+          <t>5,85; 13,76</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-24,75; -14,93</t>
+          <t>-25,03; -15,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,78</t>
+          <t>-9,36; 1,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,81; -15,05</t>
+          <t>-22,66; -14,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,51</t>
+          <t>-2,67; 5,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-22,42; -16,09</t>
+          <t>-22,66; -15,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,27</t>
+          <t>-3,85; 4,57</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,5; -17,76</t>
+          <t>-28,44; -18,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 2,02</t>
+          <t>-10,82; 1,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,34; -16,5</t>
+          <t>-24,52; -16,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 6,06</t>
+          <t>-2,86; 6,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,06; -18,32</t>
+          <t>-25,19; -18,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 4,91</t>
+          <t>-4,27; 5,24</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>11,18; 19,1</t>
+          <t>11,21; 18,62</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-55,47; -11,01</t>
+          <t>-54,03; -10,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,16</t>
+          <t>11,92; 18,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -4,73</t>
+          <t>-13,22; -4,67</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,32; 17,55</t>
+          <t>12,34; 17,46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-42,28; -9,88</t>
+          <t>-41,36; -9,77</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,56; 26,77</t>
+          <t>14,51; 26,1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-73,49; -14,81</t>
+          <t>-72,1; -14,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13,95; 23,57</t>
+          <t>14,59; 24,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -6,07</t>
+          <t>-16,26; -6,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,5; 23,36</t>
+          <t>15,64; 23,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,32; -12,91</t>
+          <t>-54,49; -12,86</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,63</t>
+          <t>-2,1; 1,58</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -0,34</t>
+          <t>-25,67; -0,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,21</t>
+          <t>-1,85; 1,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,4</t>
+          <t>-6,68; 1,39</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,92</t>
+          <t>-1,63; 0,96</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -0,04</t>
+          <t>-14,53; -0,01</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,01</t>
+          <t>-2,53; 1,95</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-29,39; -0,44</t>
+          <t>-31,08; -0,46</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,38</t>
+          <t>-2,09; 1,47</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,61</t>
+          <t>-7,63; 1,58</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,1</t>
+          <t>-1,9; 1,13</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -0,05</t>
+          <t>-17,05; -0,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,48</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,57</t>
+          <t>11,01</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,39; -6,64</t>
+          <t>-20,98; -6,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 18,02</t>
+          <t>8,25; 18,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,59; -7,92</t>
+          <t>-21,31; -8,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 12,95</t>
+          <t>5,43; 13,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; -9,14</t>
+          <t>-18,79; -9,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 13,99</t>
+          <t>7,93; 14,36</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,2; -8,14</t>
+          <t>-24,67; -7,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,69; 22,89</t>
+          <t>9,39; 22,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -9,03</t>
+          <t>-23,12; -9,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 15,1</t>
+          <t>5,79; 15,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,34; -10,7</t>
+          <t>-21,16; -10,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,78</t>
+          <t>8,84; 17,12</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-11,51</t>
+          <t>-10,77</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>-9,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-10,35</t>
+          <t>-10,11</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,55</t>
+          <t>-2,92; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,23; -4,84</t>
+          <t>-17,27; -4,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,74</t>
+          <t>-1,24; 4,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -5,31</t>
+          <t>-14,13; -5,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,23</t>
+          <t>-0,88; 4,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -6,75</t>
+          <t>-13,81; -6,54</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-13,24%</t>
+          <t>-12,39%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,69%</t>
+          <t>-10,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,47%</t>
+          <t>-11,21%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 6,62</t>
+          <t>-3,33; 6,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,99; -5,7</t>
+          <t>-19,48; -5,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,19</t>
+          <t>-1,3; 4,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -5,73</t>
+          <t>-15,01; -6,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,77</t>
+          <t>-0,95; 4,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,84; -7,6</t>
+          <t>-15,1; -7,32</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,93</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,68</t>
+          <t>8,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>8,83</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 10,12</t>
+          <t>-0,46; 9,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 14,09</t>
+          <t>3,75; 14,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 8,57</t>
+          <t>-0,44; 8,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 12,97</t>
+          <t>4,52; 12,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,93</t>
+          <t>0,97; 8,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,44</t>
+          <t>5,71; 11,97</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 12,41</t>
+          <t>-0,45; 11,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 17,37</t>
+          <t>4,34; 17,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 10,08</t>
+          <t>-0,47; 10,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 15,28</t>
+          <t>4,98; 14,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 9,37</t>
+          <t>1,07; 9,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 14,76</t>
+          <t>6,5; 14,29</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>9,27</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>7,76</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>8,63</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 20,12</t>
+          <t>8,97; 19,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 17,83</t>
+          <t>1,26; 16,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,14</t>
+          <t>2,08; 11,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 10,42</t>
+          <t>2,86; 12,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,89</t>
+          <t>6,93; 14,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 11,31</t>
+          <t>3,74; 12,53</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-5,97%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,47; 27,74</t>
+          <t>11,2; 26,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 24,31</t>
+          <t>1,6; 22,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,68</t>
+          <t>2,45; 13,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 12,43</t>
+          <t>3,3; 15,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,4; 17,77</t>
+          <t>8,2; 17,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 14,09</t>
+          <t>4,61; 15,96</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-5,37</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,78</t>
+          <t>-5,43</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-5,27</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 1,9</t>
+          <t>-14,01; 1,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 5,62</t>
+          <t>-13,24; 2,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 1,76</t>
+          <t>-8,53; 1,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 1,16</t>
+          <t>-10,79; 0,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 0,19</t>
+          <t>-9,81; -0,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 2,3</t>
+          <t>-9,68; -0,38</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-2,16%</t>
+          <t>-6,42%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-4,11%</t>
+          <t>-5,91%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-2,98%</t>
+          <t>-5,99%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 2,15</t>
+          <t>-16,11; 2,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 6,97</t>
+          <t>-15,2; 3,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 1,95</t>
+          <t>-9,06; 1,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 1,26</t>
+          <t>-11,59; -0,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 0,22</t>
+          <t>-10,97; -0,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 2,72</t>
+          <t>-10,91; -0,45</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8,93</t>
+          <t>8,73</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,49</t>
+          <t>7,39</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -0,64</t>
+          <t>-13,48; -0,82</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,87</t>
+          <t>1,41; 11,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 4,19</t>
+          <t>-7,31; 4,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,73</t>
+          <t>4,67; 13,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -0,53</t>
+          <t>-8,77; -0,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,26; 11,77</t>
+          <t>4,1; 10,89</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -0,88</t>
+          <t>-14,79; -1,06</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,75; 15,35</t>
+          <t>1,61; 13,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 4,83</t>
+          <t>-7,98; 4,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,25; 16,23</t>
+          <t>5,2; 16,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,71; -0,58</t>
+          <t>-9,74; -0,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,76</t>
+          <t>4,57; 12,76</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-2,28</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-1,67</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-25,03; -15,13</t>
+          <t>-24,96; -15,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 1,59</t>
+          <t>-6,83; 2,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,66; -14,79</t>
+          <t>-22,71; -15,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 5,8</t>
+          <t>-4,06; 1,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-22,66; -15,89</t>
+          <t>-22,18; -15,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 4,57</t>
+          <t>-4,72; 1,15</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-3,98%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>-1,26%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0,53%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -18,06</t>
+          <t>-28,5; -18,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 1,84</t>
+          <t>-7,87; 2,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -16,32</t>
+          <t>-24,54; -16,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 6,41</t>
+          <t>-4,31; 1,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,19; -18,06</t>
+          <t>-24,72; -17,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 5,24</t>
+          <t>-5,24; 1,31</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-28,99</t>
+          <t>-14,48</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-8,88</t>
+          <t>-10,28</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-20,62</t>
+          <t>-12,35</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>11,21; 18,62</t>
+          <t>11,0; 18,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-54,03; -10,78</t>
+          <t>-19,83; -9,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11,92; 18,76</t>
+          <t>11,73; 18,14</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -4,67</t>
+          <t>-14,78; -6,27</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,46</t>
+          <t>12,33; 17,51</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-41,36; -9,77</t>
+          <t>-15,44; -8,73</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-39,02%</t>
+          <t>-19,48%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-11,19%</t>
+          <t>-12,95%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-26,82%</t>
+          <t>-16,06%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,51; 26,1</t>
+          <t>14,25; 26,12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,1; -14,62</t>
+          <t>-25,96; -13,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14,59; 24,72</t>
+          <t>14,26; 23,56</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -6,04</t>
+          <t>-18,23; -8,02</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,64; 23,37</t>
+          <t>15,59; 23,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -12,86</t>
+          <t>-19,83; -11,71</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-6,91</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-1,6</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,58</t>
+          <t>-2,05; 1,46</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-25,67; -0,37</t>
+          <t>-4,49; -0,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,27</t>
+          <t>-2,08; 1,05</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,39</t>
+          <t>-2,64; 0,73</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,96</t>
+          <t>-1,55; 0,92</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -0,01</t>
+          <t>-3,08; -0,25</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-8,42%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1,36%</t>
+          <t>-1,24%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-4,64%</t>
+          <t>-1,88%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,95</t>
+          <t>-2,47; 1,79</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-31,08; -0,46</t>
+          <t>-5,42; -0,11</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,47</t>
+          <t>-2,35; 1,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,58</t>
+          <t>-2,99; 0,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,13</t>
+          <t>-1,81; 1,08</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-17,05; -0,02</t>
+          <t>-3,59; -0,29</t>
         </is>
       </c>
     </row>
